--- a/output/Data and Chart Outputs/entsog_norway_entries_daily.xlsx
+++ b/output/Data and Chart Outputs/entsog_norway_entries_daily.xlsx
@@ -155,6 +155,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Norwegian-border entry points in ENTSOG (Emden not reported) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -802,7 +803,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-04 07:34 UTC; 1826 days, 2021-10-04 to 2026-10-03</t>
+          <t>2026-10-28 00:51 UTC; 1850 days, 2021-10-04 to 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2170,7 @@
         <v>5.146864</v>
       </c>
       <c r="E60" t="n">
-        <v>16.571886</v>
+        <v>16.571887</v>
       </c>
       <c r="F60" t="n">
         <v>17.606756</v>
@@ -2195,7 +2196,7 @@
         <v>15.384895</v>
       </c>
       <c r="F61" t="n">
-        <v>6.367243</v>
+        <v>6.366209</v>
       </c>
       <c r="G61" t="n">
         <v>14.92788</v>
@@ -2213,7 +2214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1827"/>
+  <dimension ref="A1:G1851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42089,7 +42090,7 @@
         <v>164.828</v>
       </c>
       <c r="E1790" t="n">
-        <v>535.732</v>
+        <v>535.7329999999999</v>
       </c>
       <c r="F1790" t="n">
         <v>720.105</v>
@@ -42319,7 +42320,7 @@
         <v>138.355</v>
       </c>
       <c r="E1800" t="n">
-        <v>533.578</v>
+        <v>533.577</v>
       </c>
       <c r="F1800" t="n">
         <v>145.584</v>
@@ -42664,7 +42665,7 @@
         <v>131.318</v>
       </c>
       <c r="E1815" t="n">
-        <v>530.761</v>
+        <v>530.7619999999999</v>
       </c>
       <c r="F1815" t="n">
         <v>122.753</v>
@@ -42851,7 +42852,7 @@
         <v>480.135</v>
       </c>
       <c r="F1823" t="n">
-        <v>301.896</v>
+        <v>300.862</v>
       </c>
       <c r="G1823" t="n">
         <v>481.428</v>
@@ -42923,18 +42924,570 @@
         <v>761.4400000000001</v>
       </c>
       <c r="G1826" t="n">
-        <v>486.813</v>
+        <v>473.985</v>
       </c>
     </row>
     <row r="1827">
       <c r="A1827" s="4" t="n">
         <v>46298</v>
       </c>
+      <c r="B1827" t="n">
+        <v>468.567</v>
+      </c>
       <c r="C1827" t="n">
         <v>688.8390000000001</v>
       </c>
       <c r="D1827" t="n">
         <v>188.48</v>
+      </c>
+      <c r="E1827" t="n">
+        <v>526.7619999999999</v>
+      </c>
+      <c r="F1827" t="n">
+        <v>752.367</v>
+      </c>
+      <c r="G1827" t="n">
+        <v>503.917</v>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B1828" t="n">
+        <v>464.282</v>
+      </c>
+      <c r="C1828" t="n">
+        <v>694.462</v>
+      </c>
+      <c r="D1828" t="n">
+        <v>164.792</v>
+      </c>
+      <c r="E1828" t="n">
+        <v>526.39</v>
+      </c>
+      <c r="F1828" t="n">
+        <v>779.168</v>
+      </c>
+      <c r="G1828" t="n">
+        <v>488.96</v>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1829" t="n">
+        <v>464.148</v>
+      </c>
+      <c r="C1829" t="n">
+        <v>697.814</v>
+      </c>
+      <c r="D1829" t="n">
+        <v>162.799</v>
+      </c>
+      <c r="E1829" t="n">
+        <v>499.495</v>
+      </c>
+      <c r="F1829" t="n">
+        <v>753.008</v>
+      </c>
+      <c r="G1829" t="n">
+        <v>485.568</v>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1830" t="n">
+        <v>465.298</v>
+      </c>
+      <c r="C1830" t="n">
+        <v>689.105</v>
+      </c>
+      <c r="D1830" t="n">
+        <v>175.933</v>
+      </c>
+      <c r="E1830" t="n">
+        <v>499.613</v>
+      </c>
+      <c r="F1830" t="n">
+        <v>775.809</v>
+      </c>
+      <c r="G1830" t="n">
+        <v>485.992</v>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1831" t="n">
+        <v>460.217</v>
+      </c>
+      <c r="C1831" t="n">
+        <v>699.694</v>
+      </c>
+      <c r="D1831" t="n">
+        <v>182.381</v>
+      </c>
+      <c r="E1831" t="n">
+        <v>531.139</v>
+      </c>
+      <c r="F1831" t="n">
+        <v>788.208</v>
+      </c>
+      <c r="G1831" t="n">
+        <v>450.754</v>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1832" t="n">
+        <v>459.829</v>
+      </c>
+      <c r="C1832" t="n">
+        <v>700.796</v>
+      </c>
+      <c r="D1832" t="n">
+        <v>184.978</v>
+      </c>
+      <c r="E1832" t="n">
+        <v>533.105</v>
+      </c>
+      <c r="F1832" t="n">
+        <v>719.104</v>
+      </c>
+      <c r="G1832" t="n">
+        <v>339.542</v>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1833" t="n">
+        <v>458.204</v>
+      </c>
+      <c r="C1833" t="n">
+        <v>701.694</v>
+      </c>
+      <c r="D1833" t="n">
+        <v>185.452</v>
+      </c>
+      <c r="E1833" t="n">
+        <v>535.308</v>
+      </c>
+      <c r="F1833" t="n">
+        <v>774.052</v>
+      </c>
+      <c r="G1833" t="n">
+        <v>348.638</v>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B1834" t="n">
+        <v>465.223</v>
+      </c>
+      <c r="C1834" t="n">
+        <v>717.726</v>
+      </c>
+      <c r="D1834" t="n">
+        <v>174.601</v>
+      </c>
+      <c r="E1834" t="n">
+        <v>532.66</v>
+      </c>
+      <c r="F1834" t="n">
+        <v>796.496</v>
+      </c>
+      <c r="G1834" t="n">
+        <v>462.746</v>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B1835" t="n">
+        <v>456.35</v>
+      </c>
+      <c r="C1835" t="n">
+        <v>675.317</v>
+      </c>
+      <c r="D1835" t="n">
+        <v>168.443</v>
+      </c>
+      <c r="E1835" t="n">
+        <v>531.318</v>
+      </c>
+      <c r="F1835" t="n">
+        <v>792.847</v>
+      </c>
+      <c r="G1835" t="n">
+        <v>418.692</v>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1836" t="n">
+        <v>464.354</v>
+      </c>
+      <c r="C1836" t="n">
+        <v>676.379</v>
+      </c>
+      <c r="D1836" t="n">
+        <v>177.125</v>
+      </c>
+      <c r="E1836" t="n">
+        <v>529.159</v>
+      </c>
+      <c r="F1836" t="n">
+        <v>845.727</v>
+      </c>
+      <c r="G1836" t="n">
+        <v>454.351</v>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1837" t="n">
+        <v>464.306</v>
+      </c>
+      <c r="C1837" t="n">
+        <v>697.36</v>
+      </c>
+      <c r="D1837" t="n">
+        <v>197.428</v>
+      </c>
+      <c r="E1837" t="n">
+        <v>527.836</v>
+      </c>
+      <c r="F1837" t="n">
+        <v>787.6319999999999</v>
+      </c>
+      <c r="G1837" t="n">
+        <v>503.887</v>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1838" t="n">
+        <v>465.318</v>
+      </c>
+      <c r="C1838" t="n">
+        <v>681.989</v>
+      </c>
+      <c r="D1838" t="n">
+        <v>193.795</v>
+      </c>
+      <c r="E1838" t="n">
+        <v>539.048</v>
+      </c>
+      <c r="F1838" t="n">
+        <v>705.376</v>
+      </c>
+      <c r="G1838" t="n">
+        <v>509.857</v>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1839" t="n">
+        <v>465.75</v>
+      </c>
+      <c r="C1839" t="n">
+        <v>664.203</v>
+      </c>
+      <c r="D1839" t="n">
+        <v>216.883</v>
+      </c>
+      <c r="E1839" t="n">
+        <v>519.206</v>
+      </c>
+      <c r="F1839" t="n">
+        <v>758.869</v>
+      </c>
+      <c r="G1839" t="n">
+        <v>478.18</v>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1840" t="n">
+        <v>464.094</v>
+      </c>
+      <c r="C1840" t="n">
+        <v>676.303</v>
+      </c>
+      <c r="D1840" t="n">
+        <v>207.591</v>
+      </c>
+      <c r="E1840" t="n">
+        <v>518.903</v>
+      </c>
+      <c r="F1840" t="n">
+        <v>786.636</v>
+      </c>
+      <c r="G1840" t="n">
+        <v>465.965</v>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B1841" t="n">
+        <v>467.893</v>
+      </c>
+      <c r="C1841" t="n">
+        <v>693.22</v>
+      </c>
+      <c r="D1841" t="n">
+        <v>199.661</v>
+      </c>
+      <c r="E1841" t="n">
+        <v>481.274</v>
+      </c>
+      <c r="F1841" t="n">
+        <v>771.664</v>
+      </c>
+      <c r="G1841" t="n">
+        <v>464.013</v>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B1842" t="n">
+        <v>466.076</v>
+      </c>
+      <c r="C1842" t="n">
+        <v>679.111</v>
+      </c>
+      <c r="D1842" t="n">
+        <v>199.806</v>
+      </c>
+      <c r="E1842" t="n">
+        <v>523.854</v>
+      </c>
+      <c r="F1842" t="n">
+        <v>819.038</v>
+      </c>
+      <c r="G1842" t="n">
+        <v>468.891</v>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1843" t="n">
+        <v>465.879</v>
+      </c>
+      <c r="C1843" t="n">
+        <v>656.936</v>
+      </c>
+      <c r="D1843" t="n">
+        <v>183.583</v>
+      </c>
+      <c r="E1843" t="n">
+        <v>510.643</v>
+      </c>
+      <c r="F1843" t="n">
+        <v>781.751</v>
+      </c>
+      <c r="G1843" t="n">
+        <v>537.8</v>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1844" t="n">
+        <v>465.642</v>
+      </c>
+      <c r="C1844" t="n">
+        <v>566.532</v>
+      </c>
+      <c r="D1844" t="n">
+        <v>277.439</v>
+      </c>
+      <c r="E1844" t="n">
+        <v>519.537</v>
+      </c>
+      <c r="F1844" t="n">
+        <v>787.125</v>
+      </c>
+      <c r="G1844" t="n">
+        <v>527.7859999999999</v>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1845" t="n">
+        <v>466.545</v>
+      </c>
+      <c r="C1845" t="n">
+        <v>530.995</v>
+      </c>
+      <c r="D1845" t="n">
+        <v>303.38</v>
+      </c>
+      <c r="E1845" t="n">
+        <v>451.385</v>
+      </c>
+      <c r="F1845" t="n">
+        <v>715.391</v>
+      </c>
+      <c r="G1845" t="n">
+        <v>545.901</v>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1846" t="n">
+        <v>462.269</v>
+      </c>
+      <c r="C1846" t="n">
+        <v>595.903</v>
+      </c>
+      <c r="D1846" t="n">
+        <v>251.541</v>
+      </c>
+      <c r="E1846" t="n">
+        <v>492.076</v>
+      </c>
+      <c r="F1846" t="n">
+        <v>518.9450000000001</v>
+      </c>
+      <c r="G1846" t="n">
+        <v>526.426</v>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1847" t="n">
+        <v>465.693</v>
+      </c>
+      <c r="C1847" t="n">
+        <v>613.673</v>
+      </c>
+      <c r="D1847" t="n">
+        <v>247.981</v>
+      </c>
+      <c r="E1847" t="n">
+        <v>457.77</v>
+      </c>
+      <c r="F1847" t="n">
+        <v>645.319</v>
+      </c>
+      <c r="G1847" t="n">
+        <v>525.006</v>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B1848" t="n">
+        <v>483.956</v>
+      </c>
+      <c r="C1848" t="n">
+        <v>690.824</v>
+      </c>
+      <c r="D1848" t="n">
+        <v>200.518</v>
+      </c>
+      <c r="E1848" t="n">
+        <v>445.969</v>
+      </c>
+      <c r="F1848" t="n">
+        <v>664.2140000000001</v>
+      </c>
+      <c r="G1848" t="n">
+        <v>562.874</v>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B1849" t="n">
+        <v>470.464</v>
+      </c>
+      <c r="C1849" t="n">
+        <v>660.2569999999999</v>
+      </c>
+      <c r="D1849" t="n">
+        <v>183.134</v>
+      </c>
+      <c r="E1849" t="n">
+        <v>474.843</v>
+      </c>
+      <c r="F1849" t="n">
+        <v>732.03</v>
+      </c>
+      <c r="G1849" t="n">
+        <v>439.715</v>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1850" t="n">
+        <v>473.216</v>
+      </c>
+      <c r="C1850" t="n">
+        <v>741.343</v>
+      </c>
+      <c r="D1850" t="n">
+        <v>180.948</v>
+      </c>
+      <c r="E1850" t="n">
+        <v>488.687</v>
+      </c>
+      <c r="F1850" t="n">
+        <v>751.599</v>
+      </c>
+      <c r="G1850" t="n">
+        <v>419.49</v>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C1851" t="n">
+        <v>528.0069999999999</v>
+      </c>
+      <c r="D1851" t="n">
+        <v>161.317</v>
       </c>
     </row>
   </sheetData>
